--- a/out/LSTM-mamba2_repeat_3_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001255746126179583</v>
+        <v>-9.315708769287449e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1442611110704704</v>
+        <v>-0.1070196012911481</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1444964461142215</v>
+        <v>-0.107195290178011</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3946732567009245</v>
+        <v>0.2967655539730406</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6456083688718187</v>
+        <v>0.4869056184988809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02812042326221907</v>
+        <v>0.0211444468266281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3065423451550021</v>
+        <v>0.2319529869918532</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04931351286032189</v>
+        <v>0.03708028369412986</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3770398201146049</v>
+        <v>0.2849619779636297</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05991040603217279</v>
+        <v>0.04504816554161525</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4475421704479265</v>
+        <v>0.3379744971440681</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01585379450315698</v>
+        <v>0.0119208732929875</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.419262863696297</v>
+        <v>0.3167105636086252</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008806912277100704</v>
+        <v>0.00662071862793783</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4210084797726318</v>
+        <v>0.3180218968864733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01850475570110038</v>
+        <v>0.01391396089809551</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4492232894681136</v>
+        <v>0.3392374891218566</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007267497114008556</v>
+        <v>0.005462997413779955</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4452363772188809</v>
+        <v>0.336238264329596</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005173255275790373</v>
+        <v>0.003889903535221407</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4483140864969585</v>
+        <v>0.3385515840686287</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002033194689467238</v>
+        <v>0.001528059163496676</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4472028229866105</v>
+        <v>0.337714767537842</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001152601288424111</v>
+        <v>0.0008643570261933406</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.447472284519545</v>
+        <v>0.3379160715260736</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004353884615056456</v>
+        <v>0.0003261721230522456</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4471907099055846</v>
+        <v>0.3377029962801158</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002019805633622404</v>
+        <v>0.0001502354225216803</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4471577941092146</v>
+        <v>0.3376769859358545</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.088857766927358e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4470974170740922</v>
+        <v>0.3376301586008151</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.741833032797311e-05</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4470612928518341</v>
+        <v>0.3376016502520689</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4470562757250671</v>
+        <v>0.3375966368485123</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4470521482239883</v>
+        <v>0.337592291222703</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4470493470781106</v>
+        <v>0.3375889408679101</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4470439033331042</v>
+        <v>0.3375835715409224</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4470379105996738</v>
+        <v>0.3375775788074921</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4470325428110955</v>
+        <v>0.3375722110189137</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4470325795595872</v>
+        <v>0.3375722477674054</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4470326898050627</v>
+        <v>0.3375723580128809</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4470327633020463</v>
+        <v>0.3375724315098645</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4470329470445055</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.447034490481162</v>
+        <v>0.3375741586889802</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.447035960420835</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4470372098695571</v>
+        <v>0.3375768780773752</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4470385695637544</v>
+        <v>0.3375782377715725</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4470363646542451</v>
+        <v>0.3375760328620633</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.447035960420835</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4470356664329004</v>
+        <v>0.3375753346407185</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.447035335696474</v>
+        <v>0.3375750039042921</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4470350417085395</v>
+        <v>0.3375747099163576</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4470346742236211</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4470345639781456</v>
+        <v>0.3375742321859638</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4470345272296539</v>
+        <v>0.3375741954374721</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4470346742236211</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4470341964932275</v>
+        <v>0.3375738647010457</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4470351519540148</v>
+        <v>0.337574820161833</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4470347844690967</v>
+        <v>0.3375744526769149</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4470352254509987</v>
+        <v>0.3375748936588168</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4470346007266375</v>
+        <v>0.3375742689344557</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4470344169841783</v>
+        <v>0.3375740851919966</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4470340127507683</v>
+        <v>0.3375736809585865</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4470331675354564</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4470331307869647</v>
+        <v>0.3375727989947828</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4470332777809319</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4470332042839483</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4470332777809319</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4470333145294239</v>
+        <v>0.337572982737242</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4470332042839483</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4470336452658503</v>
+        <v>0.3375733134736684</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4470335350203747</v>
+        <v>0.3375732032281928</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4470334982718828</v>
+        <v>0.3375731664797009</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4470334247748992</v>
+        <v>0.3375730929827173</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4470333880264075</v>
+        <v>0.3375730562342256</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4470331675354564</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4470330940384727</v>
+        <v>0.3375727622462909</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4470330205414891</v>
+        <v>0.3375726887493073</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4470330572899811</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4470329470445055</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4470330572899811</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4470333512779155</v>
+        <v>0.3375730194857337</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692042</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692042</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.7433462078326121</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.086681742285026</v>
+        <v>-1.476581766138303</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.7433462078326121</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692042</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.7433462078326121</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.2101106495269205</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001255746126179583</v>
+        <v>-0.0001164941394447815</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1442611110704704</v>
+        <v>-0.1338293914600963</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.2101106495269205</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1443866856830884</v>
+        <v>-0.1339458855995411</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1444964461142215</v>
+        <v>-0.1340482885214546</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3946732567009245</v>
+        <v>0.3682175858966905</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6456083688718187</v>
+        <v>0.6030938745205144</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02812042326221907</v>
+        <v>0.02623542568567654</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3065423451550021</v>
+        <v>0.2867564785712897</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04931351286032189</v>
+        <v>0.04600799768922756</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3770398201146049</v>
+        <v>0.3525282928933001</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05991040603217279</v>
+        <v>0.05589397190446947</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4475421704479265</v>
+        <v>0.4183044854763414</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01585379450315698</v>
+        <v>0.01479111041347453</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.419262863696297</v>
+        <v>0.3919207482267779</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008806912277100704</v>
+        <v>0.008216247438176014</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4210084797726318</v>
+        <v>0.3935490200388678</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01850475570110038</v>
+        <v>0.01726432532893069</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4492232894681136</v>
+        <v>0.4198725835719954</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007267497114008556</v>
+        <v>0.006779434443409814</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4452363772188809</v>
+        <v>0.4161525696681747</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005173255275790373</v>
+        <v>0.004826543313620532</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4483140864969585</v>
+        <v>0.4190239094743547</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002033194689467238</v>
+        <v>0.001897405569582678</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4472028229866105</v>
+        <v>0.4179866907324311</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001152601288424111</v>
+        <v>0.001073989216906629</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.447472284519545</v>
+        <v>0.4182376974749626</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004353884615056456</v>
+        <v>0.0004060292307386027</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4471907099055846</v>
+        <v>0.4179745366696049</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002019805633622404</v>
+        <v>0.0001876680775978301</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4471577941092146</v>
+        <v>0.4179434777238725</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.088857766927358e-05</v>
+        <v>6.604462590314975e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4470974170740922</v>
+        <v>0.4178866353931197</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.741833032797311e-05</v>
+        <v>1.59873730729961e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4470612928518341</v>
+        <v>0.4178524978233464</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4470562757250671</v>
+        <v>0.4178474814412214</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4470521482239883</v>
+        <v>0.4178432812318991</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4470493470781106</v>
+        <v>0.4178402973527934</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4470439033331042</v>
+        <v>0.417834853607787</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4470379105996738</v>
+        <v>0.4178288608743567</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4470325428110955</v>
+        <v>0.4178234930857783</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4470325795595872</v>
+        <v>0.41782352983427</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4470326898050627</v>
+        <v>0.4178236400797455</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4470327633020463</v>
+        <v>0.4178237135767291</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4470329470445055</v>
+        <v>0.4178238973191883</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.447034490481162</v>
+        <v>0.4178254407558448</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.447035960420835</v>
+        <v>0.4178269106955179</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4470372098695571</v>
+        <v>0.4178281601442399</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4470385695637544</v>
+        <v>0.4178295198384372</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326121</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4470363646542451</v>
+        <v>0.4178273149289279</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5212238253023747</v>
+        <v>-0.2101106495269205</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.447035960420835</v>
+        <v>0.4178269106955179</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.417826065480206</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4470356664329004</v>
+        <v>0.4178266167075832</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.447035335696474</v>
+        <v>0.4178262859711568</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4470350417085395</v>
+        <v>0.4178259919832223</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.417826065480206</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4470346742236211</v>
+        <v>0.417825624498304</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4470345639781456</v>
+        <v>0.4178255142528284</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4470345272296539</v>
+        <v>0.4178254775043367</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.7231249087787712</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4470346742236211</v>
+        <v>0.417825624498304</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4470341964932275</v>
+        <v>0.4178251467679103</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4470351519540148</v>
+        <v>0.4178261022286976</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4470351152055231</v>
+        <v>0.417826065480206</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4470347844690967</v>
+        <v>0.4178257347437795</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4470352254509987</v>
+        <v>0.4178261757256815</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4470346007266375</v>
+        <v>0.4178255510013203</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4470344169841783</v>
+        <v>0.4178253672588612</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4470340127507683</v>
+        <v>0.4178249630254512</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4470331675354564</v>
+        <v>0.4178241178101392</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4470331307869647</v>
+        <v>0.4178240810616475</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4470332777809319</v>
+        <v>0.4178242280556148</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4470332042839483</v>
+        <v>0.4178241545586311</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4470332777809319</v>
+        <v>0.4178242280556148</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4470333145294239</v>
+        <v>0.4178242648041067</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4470332042839483</v>
+        <v>0.4178241545586311</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4470336452658503</v>
+        <v>0.4178245955405331</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4470335350203747</v>
+        <v>0.4178244852950576</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4470334982718828</v>
+        <v>0.4178244485465656</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4470334247748992</v>
+        <v>0.417824375049582</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4470333880264075</v>
+        <v>0.4178243383010903</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4470331675354564</v>
+        <v>0.4178241178101392</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4470330940384727</v>
+        <v>0.4178240443131556</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4470330205414891</v>
+        <v>0.417823970816172</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4470330572899811</v>
+        <v>0.4178240075646639</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4470329470445055</v>
+        <v>0.4178238973191883</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4470330572899811</v>
+        <v>0.4178240075646639</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5212238253023747</v>
+        <v>0.5231249087787712</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4470333512779155</v>
+        <v>0.4178243015525984</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.2494317442178726</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.160118043422699</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.09928616881370544</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.08704611659049988</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.03459744155406952</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01275914534926414</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.02781810611486435</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03179294615983963</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02246630378067493</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01899630576372147</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.009397752583026886</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.003444284200668335</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.002023570239543915</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001128114759922028</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.02206548303365707</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.01011064952692042</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01280288398265839</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.01011064952692042</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.007981456816196442</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7433462078326121</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01819721981883049</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.476581766138303</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01952716708183289</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01868151500821114</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.01702162250876427</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01463576406240463</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01262511685490608</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002928443253040314</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00120839849114418</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.006140407174825668</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01087565720081329</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01107637584209442</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.005725346505641937</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7433462078326121</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003784075379371643</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.01011064952692042</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.05102726817131042</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.03510712087154388</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01293521374464035</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001813247799873352</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005153119564056396</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7433462078326121</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0003946907818317413</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.676581766138304</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003840185701847076</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.676581766138304</v>
+        <v>0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.007139626890420914</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01071246713399887</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2101106495269205</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02689411491155624</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02758455276489258</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.04478705674409866</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.08349886536598206</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.1142764091491699</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001164941394447815</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1338293914600963</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.06978018581867218</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.04339559376239777</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.007169995456933975</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004958026111125946</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01174142584204674</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01445281505584717</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01070060208439827</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.004220098257064819</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2101106495269205</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.00932161882519722</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01338925212621689</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01269224286079407</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01233057677745819</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02044094353914261</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1339458855995411</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.05248401314020157</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1340482885214546</v>
+        <v>-0.1413091442169283</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3682175858966905</v>
+        <v>0.3648865570636502</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04582987725734711</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6030938745205144</v>
+        <v>0.5891645654616225</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02623542568567654</v>
+        <v>0.02599805399442605</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.03731434792280197</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2867564785712897</v>
+        <v>0.2756888716335613</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04600799768922756</v>
+        <v>0.04559172862032112</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.04836079478263855</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3525282928933001</v>
+        <v>0.3408657824679136</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05589397190446947</v>
+        <v>0.05538887771980253</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.03775916248559952</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4183044854763414</v>
+        <v>0.4060472145462402</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01479111041347453</v>
+        <v>0.0146571198108624</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.009297806769609451</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3919207482267779</v>
+        <v>0.3799021898981331</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008216247438176014</v>
+        <v>0.008141772306311598</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.05574547499418259</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3935490200388678</v>
+        <v>0.3815157028775709</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01726432532893069</v>
+        <v>0.01710869369217399</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.08157007396221161</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4198725835719954</v>
+        <v>0.4076019796251107</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006779434443409814</v>
+        <v>0.00671888076219409</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.07052904367446899</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4161525696681747</v>
+        <v>0.4039154514306495</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004826543313620532</v>
+        <v>0.004783419935241198</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.04424512386322021</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4190239094743547</v>
+        <v>0.4067606089131804</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001897405569582678</v>
+        <v>0.001879752983997686</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.03772692382335663</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4179866907324311</v>
+        <v>0.4057329682181124</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001073989216906629</v>
+        <v>0.001064740737904572</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02618899941444397</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4182376974749626</v>
+        <v>0.4059815984496127</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004060292307386027</v>
+        <v>0.0004025061230465574</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01871728897094727</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4179745366696049</v>
+        <v>0.4057210147862057</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001876680775978301</v>
+        <v>0.0001854661567109978</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01105179637670517</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4179434777238725</v>
+        <v>0.4056902528170303</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.604462590314975e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01381590962409973</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4178866353931197</v>
+        <v>0.4056339996036724</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.59873730729961e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01464273035526276</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4178524978233464</v>
+        <v>0.4056001935149673</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01252998411655426</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4178474814412214</v>
+        <v>0.4055951771328424</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01727616041898727</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4178432812318991</v>
+        <v>0.40559097692352</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.005445562303066254</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4178402973527934</v>
+        <v>0.4055879930444143</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.007266353815793991</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.417834853607787</v>
+        <v>0.405582549299408</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.007519472390413284</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4178288608743567</v>
+        <v>0.4055765565659776</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00597338005900383</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4178234930857783</v>
+        <v>0.4055711887773992</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01020020991563797</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.41782352983427</v>
+        <v>0.4055712255258909</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01149234920740128</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4178236400797455</v>
+        <v>0.4055713357713665</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.007131841033697128</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4178237135767291</v>
+        <v>0.4055714092683501</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02930568903684616</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4178238973191883</v>
+        <v>0.4055715930108093</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.08618402481079102</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4178254407558448</v>
+        <v>0.4055731364474657</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.05322371423244476</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4178269106955179</v>
+        <v>0.4055746063871388</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.003359429538249969</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4178281601442399</v>
+        <v>0.4055758558358608</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02344355173408985</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4178295198384372</v>
+        <v>0.4055772155300582</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02579645812511444</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9433462078326121</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4178273149289279</v>
+        <v>0.4055750106205488</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01299960911273956</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2101106495269205</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4178269106955179</v>
+        <v>0.4055746063871388</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03975681960582733</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.417826065480206</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.04462526738643646</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4178266167075832</v>
+        <v>0.4055743123992041</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.03957314044237137</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4178262859711568</v>
+        <v>0.4055739816627777</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03770671784877777</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4178259919832223</v>
+        <v>0.4055736876748433</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03872133791446686</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.417826065480206</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.03053183853626251</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.417825624498304</v>
+        <v>0.4055733201899249</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.02479428052902222</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4178255142528284</v>
+        <v>0.4055732099444493</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02781932801008224</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7231249087787712</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4178254775043367</v>
+        <v>0.4055731731959576</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.03579612821340561</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7231249087787712</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.417825624498304</v>
+        <v>0.4055733201899249</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.07164137810468674</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4178251467679103</v>
+        <v>0.4055728424595313</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.07142181694507599</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4178261022286976</v>
+        <v>0.4055737979203186</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.04608858376741409</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.417826065480206</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.03258843719959259</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4178257347437795</v>
+        <v>0.4055734304354005</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.03123730421066284</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4178261757256815</v>
+        <v>0.4055738714173024</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.03329205513000488</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4178255510013203</v>
+        <v>0.4055732466929413</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.03972144424915314</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4178253672588612</v>
+        <v>0.4055730629504821</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0488128662109375</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4178249630254512</v>
+        <v>0.4055726587170721</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.04320180416107178</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4178241178101392</v>
+        <v>0.4055718135017601</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.030218705534935</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4178240810616475</v>
+        <v>0.4055717767532684</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02881691604852676</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4178242280556148</v>
+        <v>0.4055719237472357</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02145304530858994</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4178241545586311</v>
+        <v>0.4055718502502521</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.05431471019983292</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4178242280556148</v>
+        <v>0.4055719237472357</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03491844981908798</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4178242648041067</v>
+        <v>0.4055719604957276</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03918010741472244</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4178241545586311</v>
+        <v>0.4055718502502521</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.02246683835983276</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4178245955405331</v>
+        <v>0.405572291232154</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01737532019615173</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4178244852950576</v>
+        <v>0.4055721809866785</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.005688928067684174</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4178244485465656</v>
+        <v>0.4055721442381865</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.008060179650783539</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.417824375049582</v>
+        <v>0.4055720707412029</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.008277304470539093</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4178243383010903</v>
+        <v>0.4055720339927112</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002562902867794037</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4178241178101392</v>
+        <v>0.4055718135017601</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.009694017469882965</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4178240443131556</v>
+        <v>0.4055717400047765</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.006560508161783218</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.417823970816172</v>
+        <v>0.4055716665077929</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.003972914069890976</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5231249087787712</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4178240075646639</v>
+        <v>0.4055717032562848</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.009431943297386169</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4178238973191883</v>
+        <v>0.4055715930108093</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.03399574011564255</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5231249087787712</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4178240075646639</v>
+        <v>0.4055717032562848</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.04253061860799789</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5231249087787712</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4178243015525984</v>
+        <v>0.4055719972442193</v>
       </c>
     </row>
   </sheetData>
